--- a/data/IKPA_JUNI_2026.xlsx
+++ b/data/IKPA_JUNI_2026.xlsx
@@ -4106,24 +4106,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>96.92</v>
+        <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>99.98</v>
+        <v>98.75</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
@@ -4132,16 +4132,16 @@
         <v>100</v>
       </c>
       <c r="J32" t="n">
-        <v>93.83</v>
+        <v>100</v>
       </c>
       <c r="K32" t="n">
-        <v>99.95</v>
+        <v>94.98</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N32" t="n">
         <v>100</v>
@@ -4150,16 +4150,16 @@
         <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>79.06</v>
+        <v>99</v>
       </c>
       <c r="Q32" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>98.83</v>
+        <v>99</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>39931940000</v>
+        <v>38391890000</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4197,17 +4197,17 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
@@ -4223,24 +4223,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>100</v>
+        <v>96.92</v>
       </c>
       <c r="G33" t="n">
-        <v>98.45999999999999</v>
+        <v>99.98</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
@@ -4249,16 +4249,16 @@
         <v>100</v>
       </c>
       <c r="J33" t="n">
-        <v>100</v>
+        <v>93.83</v>
       </c>
       <c r="K33" t="n">
-        <v>93.84</v>
+        <v>99.95</v>
       </c>
       <c r="L33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>100</v>
@@ -4267,16 +4267,16 @@
         <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>98.77</v>
+        <v>79.06</v>
       </c>
       <c r="Q33" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>98.77</v>
+        <v>98.83</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>14555550000</v>
+        <v>39931940000</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -4314,17 +4314,17 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
@@ -4340,24 +4340,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>96.09</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>100</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -4366,16 +4366,16 @@
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>92.17</v>
+        <v>100</v>
       </c>
       <c r="K34" t="n">
-        <v>100</v>
+        <v>93.84</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N34" t="n">
         <v>100</v>
@@ -4384,16 +4384,16 @@
         <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>78.83</v>
+        <v>98.77</v>
       </c>
       <c r="Q34" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>98.53</v>
+        <v>98.77</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4422,26 +4422,26 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>10675360000</v>
+        <v>14555550000</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
@@ -4457,24 +4457,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>100</v>
+        <v>96.09</v>
       </c>
       <c r="G35" t="n">
-        <v>98.14</v>
+        <v>100</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -4483,16 +4483,16 @@
         <v>100</v>
       </c>
       <c r="J35" t="n">
-        <v>100</v>
+        <v>92.17</v>
       </c>
       <c r="K35" t="n">
-        <v>92.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="L35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>100</v>
@@ -4501,16 +4501,16 @@
         <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>98.51000000000001</v>
+        <v>78.83</v>
       </c>
       <c r="Q35" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>98.51000000000001</v>
+        <v>98.53</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>10808640000</v>
+        <v>10675360000</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -4548,17 +4548,17 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440504)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
@@ -4574,24 +4574,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>94.89</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>100</v>
+        <v>98.14</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
@@ -4600,10 +4600,10 @@
         <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>89.78</v>
+        <v>100</v>
       </c>
       <c r="K36" t="n">
-        <v>100</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="L36" t="n">
         <v>100</v>
@@ -4618,7 +4618,7 @@
         <v>100</v>
       </c>
       <c r="P36" t="n">
-        <v>98.47</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="Q36" t="n">
         <v>100</v>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>98.47</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4656,26 +4656,26 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>20452310000</v>
+        <v>10808640000</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
@@ -4691,21 +4691,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>94.28</v>
+        <v>94.89</v>
       </c>
       <c r="G37" t="n">
         <v>100</v>
@@ -4717,7 +4717,7 @@
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>88.56</v>
+        <v>89.78</v>
       </c>
       <c r="K37" t="n">
         <v>100</v>
@@ -4735,7 +4735,7 @@
         <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>98.28</v>
+        <v>98.47</v>
       </c>
       <c r="Q37" t="n">
         <v>100</v>
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>98.28</v>
+        <v>98.47</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4773,26 +4773,26 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>128489370000</v>
+        <v>20452310000</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
@@ -4808,24 +4808,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>96.36</v>
+        <v>97.92</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
@@ -4837,13 +4837,13 @@
         <v>100</v>
       </c>
       <c r="K38" t="n">
-        <v>92.70999999999999</v>
+        <v>91.67</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N38" t="n">
         <v>100</v>
@@ -4852,16 +4852,16 @@
         <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>78.54000000000001</v>
+        <v>98.33</v>
       </c>
       <c r="Q38" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>98.18000000000001</v>
+        <v>98.33</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4890,26 +4890,26 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>1731600000</v>
+        <v>61767300000</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
@@ -4925,24 +4925,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>94.25</v>
+        <v>94.28</v>
       </c>
       <c r="G39" t="n">
-        <v>99.66</v>
+        <v>100</v>
       </c>
       <c r="H39" t="n">
         <v>100</v>
@@ -4951,10 +4951,10 @@
         <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>88.48999999999999</v>
+        <v>88.56</v>
       </c>
       <c r="K39" t="n">
-        <v>98.62</v>
+        <v>100</v>
       </c>
       <c r="L39" t="n">
         <v>100</v>
@@ -4969,7 +4969,7 @@
         <v>100</v>
       </c>
       <c r="P39" t="n">
-        <v>98</v>
+        <v>98.28</v>
       </c>
       <c r="Q39" t="n">
         <v>100</v>
@@ -4978,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>98</v>
+        <v>98.28</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5007,26 +5007,26 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>9098870000</v>
+        <v>128489370000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
@@ -5042,24 +5042,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>92.62</v>
+        <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>99.47</v>
+        <v>96.36</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
@@ -5068,34 +5068,34 @@
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>85.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="K40" t="n">
-        <v>98.41</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O40" t="n">
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>87.47</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="Q40" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>97.19</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5124,26 +5124,26 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>287629890000</v>
+        <v>1731600000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
@@ -5159,24 +5159,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>92.5</v>
+        <v>94.25</v>
       </c>
       <c r="G41" t="n">
-        <v>98.52</v>
+        <v>99.66</v>
       </c>
       <c r="H41" t="n">
         <v>100</v>
@@ -5185,10 +5185,10 @@
         <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>84.98999999999999</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>99.88</v>
+        <v>98.62</v>
       </c>
       <c r="L41" t="n">
         <v>100</v>
@@ -5197,13 +5197,13 @@
         <v>100</v>
       </c>
       <c r="N41" t="n">
-        <v>94.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="O41" t="n">
         <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>97.15000000000001</v>
+        <v>98</v>
       </c>
       <c r="Q41" t="n">
         <v>100</v>
@@ -5212,7 +5212,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>97.15000000000001</v>
+        <v>98</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5241,26 +5241,26 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>405581540000</v>
+        <v>9098870000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
@@ -5276,24 +5276,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>92.8</v>
+        <v>96.73</v>
       </c>
       <c r="G42" t="n">
-        <v>99.04000000000001</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -5302,10 +5302,10 @@
         <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>85.59999999999999</v>
+        <v>93.45</v>
       </c>
       <c r="K42" t="n">
-        <v>96.15000000000001</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="L42" t="n">
         <v>100</v>
@@ -5320,7 +5320,7 @@
         <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>97.06999999999999</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="Q42" t="n">
         <v>100</v>
@@ -5329,7 +5329,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>97.06999999999999</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>16133240000</v>
+        <v>37327090000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -5367,17 +5367,17 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
@@ -5393,24 +5393,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>92.43000000000001</v>
+        <v>92.62</v>
       </c>
       <c r="G43" t="n">
-        <v>99.18000000000001</v>
+        <v>99.47</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
@@ -5419,10 +5419,10 @@
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>84.84999999999999</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>96.72</v>
+        <v>98.41</v>
       </c>
       <c r="L43" t="n">
         <v>100</v>
@@ -5431,22 +5431,22 @@
         <v>100</v>
       </c>
       <c r="N43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>97.06999999999999</v>
+        <v>87.47</v>
       </c>
       <c r="Q43" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>97.06999999999999</v>
+        <v>97.19</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>2026</v>
       </c>
       <c r="V43" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5475,26 +5475,26 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>14214110000</v>
+        <v>287629890000</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
@@ -5510,24 +5510,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>89.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="G44" t="n">
-        <v>99.92</v>
+        <v>98.52</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
@@ -5536,10 +5536,10 @@
         <v>100</v>
       </c>
       <c r="J44" t="n">
-        <v>78.8</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>99.66</v>
+        <v>99.88</v>
       </c>
       <c r="L44" t="n">
         <v>100</v>
@@ -5548,13 +5548,13 @@
         <v>100</v>
       </c>
       <c r="N44" t="n">
-        <v>100</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="O44" t="n">
         <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>96.75</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="Q44" t="n">
         <v>100</v>
@@ -5563,7 +5563,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>96.75</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>2026</v>
       </c>
       <c r="V44" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5592,26 +5592,26 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>40484710000</v>
+        <v>405581540000</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
@@ -5632,19 +5632,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>89.62</v>
+        <v>92.8</v>
       </c>
       <c r="G45" t="n">
-        <v>98.31</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="H45" t="n">
         <v>100</v>
@@ -5653,13 +5653,13 @@
         <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>79.23</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>99.91</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="M45" t="n">
         <v>100</v>
@@ -5671,7 +5671,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="n">
-        <v>96.2</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="Q45" t="n">
         <v>100</v>
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>96.2</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>2026</v>
       </c>
       <c r="V45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>15177700000</v>
+        <v>16133240000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -5718,17 +5718,17 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
@@ -5744,24 +5744,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>88.25</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>99.54000000000001</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
@@ -5770,10 +5770,10 @@
         <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>76.48999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>98.17</v>
+        <v>96.72</v>
       </c>
       <c r="L46" t="n">
         <v>100</v>
@@ -5788,7 +5788,7 @@
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>96.11</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="Q46" t="n">
         <v>100</v>
@@ -5797,7 +5797,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>96.11</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>31225620000</v>
+        <v>14214110000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5835,17 +5835,17 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
@@ -5861,24 +5861,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>100</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>95.08</v>
+        <v>99.92</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -5887,10 +5887,10 @@
         <v>100</v>
       </c>
       <c r="J47" t="n">
-        <v>100</v>
+        <v>78.8</v>
       </c>
       <c r="K47" t="n">
-        <v>80.3</v>
+        <v>99.66</v>
       </c>
       <c r="L47" t="n">
         <v>100</v>
@@ -5905,7 +5905,7 @@
         <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>96.06</v>
+        <v>96.75</v>
       </c>
       <c r="Q47" t="n">
         <v>100</v>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>96.06</v>
+        <v>96.75</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>38391890000</v>
+        <v>40484710000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5952,17 +5952,17 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
@@ -5983,19 +5983,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>88.22</v>
+        <v>89.62</v>
       </c>
       <c r="G48" t="n">
-        <v>100</v>
+        <v>98.31</v>
       </c>
       <c r="H48" t="n">
         <v>100</v>
@@ -6004,16 +6004,16 @@
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>76.43000000000001</v>
+        <v>79.23</v>
       </c>
       <c r="K48" t="n">
-        <v>100</v>
+        <v>99.91</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>93.33</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N48" t="n">
         <v>100</v>
@@ -6022,16 +6022,16 @@
         <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>76.45999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>95.58</v>
+        <v>96.2</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6060,26 +6060,26 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>5176090000</v>
+        <v>15177700000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
@@ -6095,24 +6095,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>88.09999999999999</v>
+        <v>88.25</v>
       </c>
       <c r="G49" t="n">
-        <v>98.65000000000001</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
@@ -6121,10 +6121,10 @@
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>76.2</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>94.61</v>
+        <v>98.17</v>
       </c>
       <c r="L49" t="n">
         <v>100</v>
@@ -6139,7 +6139,7 @@
         <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>95.34999999999999</v>
+        <v>96.11</v>
       </c>
       <c r="Q49" t="n">
         <v>100</v>
@@ -6148,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>95.34999999999999</v>
+        <v>96.11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6177,26 +6177,26 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>74397990000</v>
+        <v>31225620000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
@@ -6212,24 +6212,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>96.73</v>
+        <v>88.22</v>
       </c>
       <c r="G50" t="n">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="H50" t="n">
         <v>100</v>
@@ -6238,16 +6238,16 @@
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>93.45</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>80.81</v>
+        <v>100</v>
       </c>
       <c r="L50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
         <v>100</v>
@@ -6256,16 +6256,16 @@
         <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>95.18000000000001</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="Q50" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>95.18000000000001</v>
+        <v>95.58</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6294,26 +6294,26 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>37327090000</v>
+        <v>5176090000</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
@@ -6334,19 +6334,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>95.89</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>93.37</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="H51" t="n">
         <v>100</v>
@@ -6355,16 +6355,16 @@
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>91.78</v>
+        <v>76.2</v>
       </c>
       <c r="K51" t="n">
-        <v>86.73999999999999</v>
+        <v>94.61</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N51" t="n">
         <v>100</v>
@@ -6373,16 +6373,16 @@
         <v>100</v>
       </c>
       <c r="P51" t="n">
-        <v>76.12</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="Q51" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>95.14</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>50054370000</v>
+        <v>74397990000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -6420,17 +6420,17 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
@@ -6446,24 +6446,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>93.68000000000001</v>
+        <v>95.89</v>
       </c>
       <c r="G52" t="n">
-        <v>93.70999999999999</v>
+        <v>93.37</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -6472,10 +6472,10 @@
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>87.36</v>
+        <v>91.78</v>
       </c>
       <c r="K52" t="n">
-        <v>87.42</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -6490,7 +6490,7 @@
         <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>75.59</v>
+        <v>76.12</v>
       </c>
       <c r="Q52" t="n">
         <v>80</v>
@@ -6499,7 +6499,7 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>94.48999999999999</v>
+        <v>95.14</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6528,26 +6528,26 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>7789580000</v>
+        <v>50054370000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
@@ -6563,24 +6563,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>92.40000000000001</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="H53" t="n">
         <v>100</v>
@@ -6589,16 +6589,16 @@
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>100</v>
+        <v>87.36</v>
       </c>
       <c r="K53" t="n">
-        <v>69.59999999999999</v>
+        <v>87.42</v>
       </c>
       <c r="L53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>100</v>
@@ -6607,16 +6607,16 @@
         <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>93.92</v>
+        <v>75.59</v>
       </c>
       <c r="Q53" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>93.92</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6645,26 +6645,26 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>61767300000</v>
+        <v>7789580000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
@@ -6680,24 +6680,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>87.65000000000001</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>96.15000000000001</v>
+        <v>94.77</v>
       </c>
       <c r="H54" t="n">
         <v>100</v>
@@ -6706,10 +6706,10 @@
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>75.29000000000001</v>
+        <v>89.36</v>
       </c>
       <c r="K54" t="n">
-        <v>84.61</v>
+        <v>79.09</v>
       </c>
       <c r="L54" t="n">
         <v>100</v>
@@ -6724,7 +6724,7 @@
         <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>93.22</v>
+        <v>94.22</v>
       </c>
       <c r="Q54" t="n">
         <v>100</v>
@@ -6733,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>93.22</v>
+        <v>94.22</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6762,26 +6762,26 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>13427580000</v>
+        <v>114852670000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
@@ -6802,19 +6802,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>82.70999999999999</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>99.05</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -6823,16 +6823,16 @@
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>65.42</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>98.09999999999999</v>
+        <v>84.61</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N55" t="n">
         <v>100</v>
@@ -6841,16 +6841,16 @@
         <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>74.43000000000001</v>
+        <v>93.22</v>
       </c>
       <c r="Q55" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>93.04000000000001</v>
+        <v>93.22</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6879,26 +6879,26 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>9731020000</v>
+        <v>13427580000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
@@ -6919,19 +6919,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>86.23999999999999</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>95.86</v>
+        <v>99.05</v>
       </c>
       <c r="H56" t="n">
         <v>100</v>
@@ -6940,16 +6940,16 @@
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>72.48</v>
+        <v>65.42</v>
       </c>
       <c r="K56" t="n">
-        <v>83.44</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>100</v>
@@ -6958,16 +6958,16 @@
         <v>100</v>
       </c>
       <c r="P56" t="n">
-        <v>92.56</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="Q56" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>92.56</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6996,26 +6996,26 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>20589110000</v>
+        <v>9731020000</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
@@ -7036,19 +7036,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>100</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>84.53</v>
+        <v>95.86</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
@@ -7057,16 +7057,16 @@
         <v>100</v>
       </c>
       <c r="J57" t="n">
-        <v>100</v>
+        <v>72.48</v>
       </c>
       <c r="K57" t="n">
-        <v>69.05</v>
+        <v>83.44</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N57" t="n">
         <v>100</v>
@@ -7075,16 +7075,16 @@
         <v>100</v>
       </c>
       <c r="P57" t="n">
-        <v>73.81</v>
+        <v>92.56</v>
       </c>
       <c r="Q57" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>92.26000000000001</v>
+        <v>92.56</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>15707450000</v>
+        <v>20589110000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -7122,17 +7122,17 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
@@ -7153,19 +7153,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>85.63</v>
+        <v>100</v>
       </c>
       <c r="G58" t="n">
-        <v>94.89</v>
+        <v>84.53</v>
       </c>
       <c r="H58" t="n">
         <v>100</v>
@@ -7174,10 +7174,10 @@
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>71.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="K58" t="n">
-        <v>89.77</v>
+        <v>69.05</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
         <v>100</v>
       </c>
       <c r="P58" t="n">
-        <v>73.64</v>
+        <v>73.81</v>
       </c>
       <c r="Q58" t="n">
         <v>80</v>
@@ -7201,7 +7201,7 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>92.05</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7230,26 +7230,26 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>5671610000</v>
+        <v>15707450000</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
@@ -7265,24 +7265,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>94.68000000000001</v>
+        <v>85.63</v>
       </c>
       <c r="G59" t="n">
-        <v>91.95999999999999</v>
+        <v>94.89</v>
       </c>
       <c r="H59" t="n">
         <v>100</v>
@@ -7291,16 +7291,16 @@
         <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>89.36</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>67.84</v>
+        <v>89.77</v>
       </c>
       <c r="L59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
         <v>100</v>
@@ -7309,16 +7309,16 @@
         <v>100</v>
       </c>
       <c r="P59" t="n">
-        <v>91.97</v>
+        <v>73.64</v>
       </c>
       <c r="Q59" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>91.97</v>
+        <v>92.05</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7347,26 +7347,26 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>114852670000</v>
+        <v>5671610000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>

--- a/data/IKPA_JUNI_2026.xlsx
+++ b/data/IKPA_JUNI_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE67"/>
+  <dimension ref="A1:AE66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,7 +587,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -596,17 +596,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -678,33 +678,33 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>5127100000</v>
+        <v>31572500000</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>PN BATURAJA (099228)</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -713,17 +713,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -795,26 +795,26 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>970430000</v>
+        <v>11480750000</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440506)</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1213,10 +1213,10 @@
         <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
@@ -1225,10 +1225,10 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q7" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1263,33 +1263,33 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>3127760000</v>
+        <v>64847500000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1298,17 +1298,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1330,10 +1330,10 @@
         <v>100</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
@@ -1342,10 +1342,10 @@
         <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q8" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1380,26 +1380,26 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>31572500000</v>
+        <v>139911100000</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK (692625)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -1757,7 +1757,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1848,33 +1848,33 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>11480750000</v>
+        <v>3127760000</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1915,10 +1915,10 @@
         <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>100</v>
@@ -1927,10 +1927,10 @@
         <v>100</v>
       </c>
       <c r="P13" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q13" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1965,26 +1965,26 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>142639230000</v>
+        <v>970430000</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>90057130000</v>
+        <v>87620360000</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2936,24 +2936,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>100</v>
+        <v>99.92</v>
       </c>
       <c r="H22" t="n">
         <v>100</v>
@@ -2965,13 +2965,13 @@
         <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>100</v>
+        <v>99.84</v>
       </c>
       <c r="L22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>100</v>
@@ -2980,16 +2980,16 @@
         <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>100</v>
+        <v>79.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>2026</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>64847500000</v>
+        <v>67270440000</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -3027,24 +3027,24 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (401944)</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3053,60 +3053,60 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="H23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I23" t="n">
+        <v>100</v>
+      </c>
+      <c r="J23" t="n">
+        <v>100</v>
+      </c>
+      <c r="K23" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="L23" t="n">
+        <v>100</v>
+      </c>
+      <c r="M23" t="n">
+        <v>100</v>
+      </c>
+      <c r="N23" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="O23" t="n">
+        <v>100</v>
+      </c>
+      <c r="P23" t="n">
         <v>99.92</v>
       </c>
-      <c r="H23" t="n">
-        <v>100</v>
-      </c>
-      <c r="I23" t="n">
-        <v>100</v>
-      </c>
-      <c r="J23" t="n">
-        <v>100</v>
-      </c>
-      <c r="K23" t="n">
-        <v>99.84</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>100</v>
-      </c>
-      <c r="O23" t="n">
-        <v>100</v>
-      </c>
-      <c r="P23" t="n">
-        <v>79.97</v>
-      </c>
       <c r="Q23" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>99.95999999999999</v>
+        <v>99.92</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>2026</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3135,33 +3135,33 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>67124350000</v>
+        <v>18312800000</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418456)</t>
+          <t>KEJARI  OKU (007130)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3170,24 +3170,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>99.87</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="H24" t="n">
         <v>100</v>
@@ -3199,31 +3199,31 @@
         <v>100</v>
       </c>
       <c r="K24" t="n">
-        <v>99.73999999999999</v>
+        <v>99.63</v>
       </c>
       <c r="L24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>99.75</v>
+        <v>100</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
       </c>
       <c r="P24" t="n">
-        <v>99.92</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>99.92</v>
+        <v>99.91</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>2026</v>
       </c>
       <c r="V24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3252,33 +3252,33 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>18312800000</v>
+        <v>43471570000</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>KEJARI  OKU (007130)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3292,19 +3292,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>99.81999999999999</v>
+        <v>99.72</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
@@ -3316,7 +3316,7 @@
         <v>100</v>
       </c>
       <c r="K25" t="n">
-        <v>99.63</v>
+        <v>99.44</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3331,7 +3331,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="n">
-        <v>79.93000000000001</v>
+        <v>79.89</v>
       </c>
       <c r="Q25" t="n">
         <v>80</v>
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>99.91</v>
+        <v>99.86</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>2026</v>
       </c>
       <c r="V25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3369,33 +3369,33 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>43471570000</v>
+        <v>38902730000</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3404,24 +3404,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>99.72</v>
+        <v>99.63</v>
       </c>
       <c r="H26" t="n">
         <v>100</v>
@@ -3433,7 +3433,7 @@
         <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>99.44</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3442,13 +3442,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>100</v>
+        <v>99.77</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
       </c>
       <c r="P26" t="n">
-        <v>79.89</v>
+        <v>79.88</v>
       </c>
       <c r="Q26" t="n">
         <v>80</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>99.86</v>
+        <v>99.84</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>2026</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3486,33 +3486,33 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>38902730000</v>
+        <v>10710500000</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3521,27 +3521,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>99.63</v>
+        <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>100</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>100</v>
@@ -3550,31 +3550,31 @@
         <v>100</v>
       </c>
       <c r="K27" t="n">
-        <v>99.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N27" t="n">
-        <v>99.77</v>
+        <v>100</v>
       </c>
       <c r="O27" t="n">
-        <v>100</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>79.88</v>
+        <v>99.67</v>
       </c>
       <c r="Q27" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>99.84</v>
+        <v>99.67</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>2026</v>
       </c>
       <c r="V27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>10710500000</v>
+        <v>729500000</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3612,24 +3612,24 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3638,27 +3638,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>100</v>
+        <v>99.48</v>
       </c>
       <c r="H28" t="n">
-        <v>98.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="I28" t="n">
         <v>100</v>
@@ -3667,7 +3667,7 @@
         <v>100</v>
       </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>97.92</v>
       </c>
       <c r="L28" t="n">
         <v>100</v>
@@ -3679,10 +3679,10 @@
         <v>100</v>
       </c>
       <c r="O28" t="n">
-        <v>98.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="P28" t="n">
-        <v>99.67</v>
+        <v>99.58</v>
       </c>
       <c r="Q28" t="n">
         <v>100</v>
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>99.67</v>
+        <v>99.58</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>2026</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3720,33 +3720,33 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>729500000</v>
+        <v>105914680000</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3755,24 +3755,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>99.48</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -3784,7 +3784,7 @@
         <v>100</v>
       </c>
       <c r="K29" t="n">
-        <v>97.92</v>
+        <v>97.28</v>
       </c>
       <c r="L29" t="n">
         <v>100</v>
@@ -3793,13 +3793,13 @@
         <v>100</v>
       </c>
       <c r="N29" t="n">
-        <v>100</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>99.58</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="Q29" t="n">
         <v>100</v>
@@ -3808,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>99.58</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>2026</v>
       </c>
       <c r="V29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3837,33 +3837,33 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>105914680000</v>
+        <v>9346940000</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3877,19 +3877,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>100</v>
       </c>
       <c r="G30" t="n">
-        <v>99.31999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
@@ -3901,31 +3901,31 @@
         <v>100</v>
       </c>
       <c r="K30" t="n">
-        <v>97.28</v>
+        <v>96.8</v>
       </c>
       <c r="L30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>99.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>99.45999999999999</v>
+        <v>79.36</v>
       </c>
       <c r="Q30" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>99.45999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>2026</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>9346940000</v>
+        <v>3898470000</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3963,24 +3963,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3989,24 +3989,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>98.40000000000001</v>
+        <v>98.75</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
@@ -4018,13 +4018,13 @@
         <v>100</v>
       </c>
       <c r="K31" t="n">
-        <v>96.8</v>
+        <v>94.98</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N31" t="n">
         <v>100</v>
@@ -4033,16 +4033,16 @@
         <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>79.36</v>
+        <v>99</v>
       </c>
       <c r="Q31" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>99.2</v>
+        <v>99</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>2026</v>
       </c>
       <c r="V31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -4071,33 +4071,33 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>3898470000</v>
+        <v>38391890000</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4106,24 +4106,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>100</v>
+        <v>96.92</v>
       </c>
       <c r="G32" t="n">
-        <v>98.75</v>
+        <v>99.98</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
@@ -4132,16 +4132,16 @@
         <v>100</v>
       </c>
       <c r="J32" t="n">
-        <v>100</v>
+        <v>93.83</v>
       </c>
       <c r="K32" t="n">
-        <v>94.98</v>
+        <v>99.95</v>
       </c>
       <c r="L32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>100</v>
@@ -4150,16 +4150,16 @@
         <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>99</v>
+        <v>79.06</v>
       </c>
       <c r="Q32" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>99</v>
+        <v>98.83</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>2026</v>
       </c>
       <c r="V32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>38391890000</v>
+        <v>39931940000</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4197,24 +4197,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4223,24 +4223,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>96.92</v>
+        <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>99.98</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
@@ -4249,16 +4249,16 @@
         <v>100</v>
       </c>
       <c r="J33" t="n">
-        <v>93.83</v>
+        <v>100</v>
       </c>
       <c r="K33" t="n">
-        <v>99.95</v>
+        <v>93.84</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N33" t="n">
         <v>100</v>
@@ -4267,16 +4267,16 @@
         <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>79.06</v>
+        <v>98.77</v>
       </c>
       <c r="Q33" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>98.83</v>
+        <v>98.77</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>2026</v>
       </c>
       <c r="V33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4305,33 +4305,33 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>39931940000</v>
+        <v>3127020000</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4340,24 +4340,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>100</v>
+        <v>96.09</v>
       </c>
       <c r="G34" t="n">
-        <v>98.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -4366,16 +4366,16 @@
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>100</v>
+        <v>92.17</v>
       </c>
       <c r="K34" t="n">
-        <v>93.84</v>
+        <v>100</v>
       </c>
       <c r="L34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>100</v>
@@ -4384,16 +4384,16 @@
         <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>98.77</v>
+        <v>78.83</v>
       </c>
       <c r="Q34" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>98.77</v>
+        <v>98.53</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>2026</v>
       </c>
       <c r="V34" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4422,33 +4422,33 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>14555550000</v>
+        <v>5172810000</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4457,24 +4457,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>96.09</v>
+        <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>100</v>
+        <v>98.14</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -4483,16 +4483,16 @@
         <v>100</v>
       </c>
       <c r="J35" t="n">
-        <v>92.17</v>
+        <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>100</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N35" t="n">
         <v>100</v>
@@ -4501,16 +4501,16 @@
         <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>78.83</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="Q35" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>98.53</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>2026</v>
       </c>
       <c r="V35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4539,33 +4539,33 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>10675360000</v>
+        <v>10808640000</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4574,24 +4574,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>100</v>
+        <v>94.89</v>
       </c>
       <c r="G36" t="n">
-        <v>98.14</v>
+        <v>100</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
@@ -4600,10 +4600,10 @@
         <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>100</v>
+        <v>89.78</v>
       </c>
       <c r="K36" t="n">
-        <v>92.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="L36" t="n">
         <v>100</v>
@@ -4618,7 +4618,7 @@
         <v>100</v>
       </c>
       <c r="P36" t="n">
-        <v>98.51000000000001</v>
+        <v>98.47</v>
       </c>
       <c r="Q36" t="n">
         <v>100</v>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>98.51000000000001</v>
+        <v>98.47</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>2026</v>
       </c>
       <c r="V36" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4656,33 +4656,33 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>10808640000</v>
+        <v>20452310000</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440504)</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4691,24 +4691,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>94.89</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>100</v>
+        <v>97.92</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -4717,10 +4717,10 @@
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>89.78</v>
+        <v>100</v>
       </c>
       <c r="K37" t="n">
-        <v>100</v>
+        <v>91.67</v>
       </c>
       <c r="L37" t="n">
         <v>100</v>
@@ -4735,7 +4735,7 @@
         <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>98.47</v>
+        <v>98.33</v>
       </c>
       <c r="Q37" t="n">
         <v>100</v>
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>98.47</v>
+        <v>98.33</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>2026</v>
       </c>
       <c r="V37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4773,33 +4773,33 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>20452310000</v>
+        <v>61767300000</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4808,24 +4808,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>100</v>
+        <v>94.28</v>
       </c>
       <c r="G38" t="n">
-        <v>97.92</v>
+        <v>100</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
@@ -4834,10 +4834,10 @@
         <v>100</v>
       </c>
       <c r="J38" t="n">
-        <v>100</v>
+        <v>88.56</v>
       </c>
       <c r="K38" t="n">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="L38" t="n">
         <v>100</v>
@@ -4852,7 +4852,7 @@
         <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>98.33</v>
+        <v>98.28</v>
       </c>
       <c r="Q38" t="n">
         <v>100</v>
@@ -4861,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>98.33</v>
+        <v>98.28</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>2026</v>
       </c>
       <c r="V38" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>61767300000</v>
+        <v>128489370000</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4899,24 +4899,24 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4925,24 +4925,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>94.28</v>
+        <v>100</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>96.36</v>
       </c>
       <c r="H39" t="n">
         <v>100</v>
@@ -4951,16 +4951,16 @@
         <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>88.56</v>
+        <v>100</v>
       </c>
       <c r="K39" t="n">
-        <v>100</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>100</v>
@@ -4969,16 +4969,16 @@
         <v>100</v>
       </c>
       <c r="P39" t="n">
-        <v>98.28</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="Q39" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>98.28</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>2026</v>
       </c>
       <c r="V39" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -5007,33 +5007,33 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>128489370000</v>
+        <v>1731600000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5047,19 +5047,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>100</v>
+        <v>94.25</v>
       </c>
       <c r="G40" t="n">
-        <v>96.36</v>
+        <v>99.66</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
@@ -5068,16 +5068,16 @@
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>100</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>92.70999999999999</v>
+        <v>98.62</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N40" t="n">
         <v>100</v>
@@ -5086,16 +5086,16 @@
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>78.54000000000001</v>
+        <v>98</v>
       </c>
       <c r="Q40" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>98.18000000000001</v>
+        <v>98</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>2026</v>
       </c>
       <c r="V40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>1731600000</v>
+        <v>9098870000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -5133,24 +5133,24 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5159,24 +5159,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>94.25</v>
+        <v>96.73</v>
       </c>
       <c r="G41" t="n">
-        <v>99.66</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="H41" t="n">
         <v>100</v>
@@ -5185,10 +5185,10 @@
         <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>88.48999999999999</v>
+        <v>93.45</v>
       </c>
       <c r="K41" t="n">
-        <v>98.62</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="L41" t="n">
         <v>100</v>
@@ -5203,7 +5203,7 @@
         <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>98</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="Q41" t="n">
         <v>100</v>
@@ -5212,7 +5212,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>98</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>2026</v>
       </c>
       <c r="V41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -5241,33 +5241,33 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>9098870000</v>
+        <v>37327090000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5276,24 +5276,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>96.73</v>
+        <v>92.62</v>
       </c>
       <c r="G42" t="n">
-        <v>98.70999999999999</v>
+        <v>99.47</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -5302,10 +5302,10 @@
         <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>93.45</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>94.84999999999999</v>
+        <v>98.41</v>
       </c>
       <c r="L42" t="n">
         <v>100</v>
@@ -5314,22 +5314,22 @@
         <v>100</v>
       </c>
       <c r="N42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>97.98999999999999</v>
+        <v>87.47</v>
       </c>
       <c r="Q42" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>97.98999999999999</v>
+        <v>97.19</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>2026</v>
       </c>
       <c r="V42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5358,33 +5358,33 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>37327090000</v>
+        <v>287629890000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5398,19 +5398,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>92.62</v>
+        <v>92.5</v>
       </c>
       <c r="G43" t="n">
-        <v>99.47</v>
+        <v>98.52</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
@@ -5419,10 +5419,10 @@
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>85.23999999999999</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>98.41</v>
+        <v>99.88</v>
       </c>
       <c r="L43" t="n">
         <v>100</v>
@@ -5431,22 +5431,22 @@
         <v>100</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="O43" t="n">
         <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>87.47</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="Q43" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>97.19</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>2026</v>
       </c>
       <c r="V43" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>287629890000</v>
+        <v>405581540000</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -5484,24 +5484,24 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5510,24 +5510,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>92.5</v>
+        <v>92.8</v>
       </c>
       <c r="G44" t="n">
-        <v>98.52</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
@@ -5536,10 +5536,10 @@
         <v>100</v>
       </c>
       <c r="J44" t="n">
-        <v>84.98999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>99.88</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="L44" t="n">
         <v>100</v>
@@ -5548,13 +5548,13 @@
         <v>100</v>
       </c>
       <c r="N44" t="n">
-        <v>94.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="O44" t="n">
         <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>97.15000000000001</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="Q44" t="n">
         <v>100</v>
@@ -5563,7 +5563,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>97.15000000000001</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>2026</v>
       </c>
       <c r="V44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5592,33 +5592,33 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>405581540000</v>
+        <v>16133240000</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5627,24 +5627,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>92.8</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>99.04000000000001</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H45" t="n">
         <v>100</v>
@@ -5653,10 +5653,10 @@
         <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>85.59999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>96.15000000000001</v>
+        <v>96.72</v>
       </c>
       <c r="L45" t="n">
         <v>100</v>
@@ -5709,7 +5709,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>16133240000</v>
+        <v>14214110000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -5718,24 +5718,24 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5744,24 +5744,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>92.43000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>99.18000000000001</v>
+        <v>99.92</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
@@ -5770,10 +5770,10 @@
         <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>84.84999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="K46" t="n">
-        <v>96.72</v>
+        <v>99.66</v>
       </c>
       <c r="L46" t="n">
         <v>100</v>
@@ -5788,7 +5788,7 @@
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>97.06999999999999</v>
+        <v>96.75</v>
       </c>
       <c r="Q46" t="n">
         <v>100</v>
@@ -5797,7 +5797,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>97.06999999999999</v>
+        <v>96.75</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>2026</v>
       </c>
       <c r="V46" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>14214110000</v>
+        <v>40484710000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5835,24 +5835,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5861,24 +5861,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>89.40000000000001</v>
+        <v>89.62</v>
       </c>
       <c r="G47" t="n">
-        <v>99.92</v>
+        <v>98.31</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -5887,13 +5887,13 @@
         <v>100</v>
       </c>
       <c r="J47" t="n">
-        <v>78.8</v>
+        <v>79.23</v>
       </c>
       <c r="K47" t="n">
-        <v>99.66</v>
+        <v>99.91</v>
       </c>
       <c r="L47" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="M47" t="n">
         <v>100</v>
@@ -5905,7 +5905,7 @@
         <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>96.75</v>
+        <v>96.2</v>
       </c>
       <c r="Q47" t="n">
         <v>100</v>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>96.75</v>
+        <v>96.2</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>2026</v>
       </c>
       <c r="V47" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>40484710000</v>
+        <v>15177700000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5952,24 +5952,24 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5978,24 +5978,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>89.62</v>
+        <v>88.25</v>
       </c>
       <c r="G48" t="n">
-        <v>98.31</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H48" t="n">
         <v>100</v>
@@ -6004,13 +6004,13 @@
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>79.23</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>99.91</v>
+        <v>98.17</v>
       </c>
       <c r="L48" t="n">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="M48" t="n">
         <v>100</v>
@@ -6022,7 +6022,7 @@
         <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>96.2</v>
+        <v>96.11</v>
       </c>
       <c r="Q48" t="n">
         <v>100</v>
@@ -6031,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>96.2</v>
+        <v>96.11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>2026</v>
       </c>
       <c r="V48" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>15177700000</v>
+        <v>31225620000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -6069,24 +6069,24 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6095,24 +6095,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>88.25</v>
+        <v>88.22</v>
       </c>
       <c r="G49" t="n">
-        <v>99.54000000000001</v>
+        <v>100</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
@@ -6121,16 +6121,16 @@
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>76.48999999999999</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>98.17</v>
+        <v>100</v>
       </c>
       <c r="L49" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>100</v>
@@ -6139,16 +6139,16 @@
         <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>96.11</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="Q49" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>96.11</v>
+        <v>95.58</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>2026</v>
       </c>
       <c r="V49" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -6177,33 +6177,33 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>31225620000</v>
+        <v>5176090000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6212,24 +6212,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>88.22</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>100</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="H50" t="n">
         <v>100</v>
@@ -6238,16 +6238,16 @@
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>76.43000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="K50" t="n">
-        <v>100</v>
+        <v>94.61</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N50" t="n">
         <v>100</v>
@@ -6256,16 +6256,16 @@
         <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>76.45999999999999</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="Q50" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>95.58</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>2026</v>
       </c>
       <c r="V50" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -6294,33 +6294,33 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>5176090000</v>
+        <v>74397990000</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6334,19 +6334,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>88.09999999999999</v>
+        <v>95.89</v>
       </c>
       <c r="G51" t="n">
-        <v>98.65000000000001</v>
+        <v>93.37</v>
       </c>
       <c r="H51" t="n">
         <v>100</v>
@@ -6355,16 +6355,16 @@
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>76.2</v>
+        <v>91.78</v>
       </c>
       <c r="K51" t="n">
-        <v>94.61</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
         <v>100</v>
@@ -6373,16 +6373,16 @@
         <v>100</v>
       </c>
       <c r="P51" t="n">
-        <v>95.34999999999999</v>
+        <v>76.12</v>
       </c>
       <c r="Q51" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>95.34999999999999</v>
+        <v>95.14</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>2026</v>
       </c>
       <c r="V51" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>74397990000</v>
+        <v>50054370000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -6420,24 +6420,24 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6446,24 +6446,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>95.89</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>93.37</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -6472,10 +6472,10 @@
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>91.78</v>
+        <v>87.36</v>
       </c>
       <c r="K52" t="n">
-        <v>86.73999999999999</v>
+        <v>87.42</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -6490,7 +6490,7 @@
         <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>76.12</v>
+        <v>75.59</v>
       </c>
       <c r="Q52" t="n">
         <v>80</v>
@@ -6499,7 +6499,7 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>95.14</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>2026</v>
       </c>
       <c r="V52" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -6528,33 +6528,33 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>50054370000</v>
+        <v>7789580000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6563,24 +6563,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>93.68000000000001</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>93.70999999999999</v>
+        <v>94.77</v>
       </c>
       <c r="H53" t="n">
         <v>100</v>
@@ -6589,16 +6589,16 @@
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>87.36</v>
+        <v>89.36</v>
       </c>
       <c r="K53" t="n">
-        <v>87.42</v>
+        <v>79.09</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N53" t="n">
         <v>100</v>
@@ -6607,16 +6607,16 @@
         <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>75.59</v>
+        <v>94.22</v>
       </c>
       <c r="Q53" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>94.48999999999999</v>
+        <v>94.22</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>2026</v>
       </c>
       <c r="V53" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -6645,33 +6645,33 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>7789580000</v>
+        <v>114852670000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6680,24 +6680,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>94.68000000000001</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>94.77</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H54" t="n">
         <v>100</v>
@@ -6706,10 +6706,10 @@
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>89.36</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>79.09</v>
+        <v>84.61</v>
       </c>
       <c r="L54" t="n">
         <v>100</v>
@@ -6724,7 +6724,7 @@
         <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>94.22</v>
+        <v>93.22</v>
       </c>
       <c r="Q54" t="n">
         <v>100</v>
@@ -6733,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>94.22</v>
+        <v>93.22</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>2026</v>
       </c>
       <c r="V54" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6762,33 +6762,33 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>114852670000</v>
+        <v>13427580000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6802,19 +6802,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>87.65000000000001</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>96.15000000000001</v>
+        <v>99.05</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -6823,16 +6823,16 @@
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>75.29000000000001</v>
+        <v>65.42</v>
       </c>
       <c r="K55" t="n">
-        <v>84.61</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
         <v>100</v>
@@ -6841,16 +6841,16 @@
         <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>93.22</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="Q55" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>93.22</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>2026</v>
       </c>
       <c r="V55" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6879,33 +6879,33 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>13427580000</v>
+        <v>9731020000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6919,19 +6919,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>82.70999999999999</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>99.05</v>
+        <v>95.86</v>
       </c>
       <c r="H56" t="n">
         <v>100</v>
@@ -6940,16 +6940,16 @@
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>65.42</v>
+        <v>72.48</v>
       </c>
       <c r="K56" t="n">
-        <v>98.09999999999999</v>
+        <v>83.44</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N56" t="n">
         <v>100</v>
@@ -6958,16 +6958,16 @@
         <v>100</v>
       </c>
       <c r="P56" t="n">
-        <v>74.43000000000001</v>
+        <v>92.56</v>
       </c>
       <c r="Q56" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>93.04000000000001</v>
+        <v>92.56</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>2026</v>
       </c>
       <c r="V56" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -6996,33 +6996,33 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>9731020000</v>
+        <v>20589110000</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -7036,19 +7036,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>86.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>95.86</v>
+        <v>84.53</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
@@ -7057,16 +7057,16 @@
         <v>100</v>
       </c>
       <c r="J57" t="n">
-        <v>72.48</v>
+        <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>83.44</v>
+        <v>69.05</v>
       </c>
       <c r="L57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>100</v>
@@ -7075,16 +7075,16 @@
         <v>100</v>
       </c>
       <c r="P57" t="n">
-        <v>92.56</v>
+        <v>73.81</v>
       </c>
       <c r="Q57" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>92.56</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>2026</v>
       </c>
       <c r="V57" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>20589110000</v>
+        <v>15707450000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -7122,24 +7122,24 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -7148,24 +7148,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>79.72</v>
       </c>
       <c r="G58" t="n">
-        <v>84.53</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H58" t="n">
         <v>100</v>
@@ -7174,16 +7174,16 @@
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>100</v>
+        <v>59.43</v>
       </c>
       <c r="K58" t="n">
-        <v>69.05</v>
+        <v>91.58</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N58" t="n">
         <v>100</v>
@@ -7192,16 +7192,16 @@
         <v>100</v>
       </c>
       <c r="P58" t="n">
-        <v>73.81</v>
+        <v>92.23</v>
       </c>
       <c r="Q58" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>92.26000000000001</v>
+        <v>92.23</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>2026</v>
       </c>
       <c r="V58" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>15707450000</v>
+        <v>29335310000</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -7239,24 +7239,24 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>2026</v>
       </c>
       <c r="V59" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>2026</v>
       </c>
       <c r="V60" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -7499,24 +7499,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>695184</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>79.63</v>
+        <v>75.98</v>
       </c>
       <c r="G61" t="n">
-        <v>93.34999999999999</v>
+        <v>97.11</v>
       </c>
       <c r="H61" t="n">
         <v>100</v>
@@ -7525,16 +7525,16 @@
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>59.26</v>
+        <v>51.95</v>
       </c>
       <c r="K61" t="n">
-        <v>86.69</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N61" t="n">
         <v>100</v>
@@ -7543,16 +7543,16 @@
         <v>100</v>
       </c>
       <c r="P61" t="n">
-        <v>71.23</v>
+        <v>90.48</v>
       </c>
       <c r="Q61" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>89.03</v>
+        <v>90.48</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>2026</v>
       </c>
       <c r="V61" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>7585360000</v>
+        <v>6722660000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -7590,24 +7590,24 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>KANTOR KEMENHAJ OKUS</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>KANTOR KEMENHAJ OKUS (695184)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>KANTOR KEMENHAJ OKUS</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -7621,19 +7621,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>71.36</v>
+        <v>79.62</v>
       </c>
       <c r="G62" t="n">
-        <v>99.48</v>
+        <v>95.36</v>
       </c>
       <c r="H62" t="n">
         <v>100</v>
@@ -7642,16 +7642,16 @@
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>42.72</v>
+        <v>59.23</v>
       </c>
       <c r="K62" t="n">
-        <v>98.95</v>
+        <v>81.44</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N62" t="n">
         <v>100</v>
@@ -7660,16 +7660,16 @@
         <v>100</v>
       </c>
       <c r="P62" t="n">
-        <v>71.2</v>
+        <v>90.17</v>
       </c>
       <c r="Q62" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>89</v>
+        <v>90.17</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>2026</v>
       </c>
       <c r="V62" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -7698,33 +7698,33 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>13489830000</v>
+        <v>6368000000</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -7733,24 +7733,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>695176</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>72.23</v>
+        <v>79.63</v>
       </c>
       <c r="G63" t="n">
-        <v>96.34</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="H63" t="n">
         <v>100</v>
@@ -7759,16 +7759,16 @@
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>44.45</v>
+        <v>59.26</v>
       </c>
       <c r="K63" t="n">
-        <v>85.34999999999999</v>
+        <v>86.69</v>
       </c>
       <c r="L63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
         <v>100</v>
@@ -7777,16 +7777,16 @@
         <v>100</v>
       </c>
       <c r="P63" t="n">
-        <v>88.73999999999999</v>
+        <v>71.23</v>
       </c>
       <c r="Q63" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>88.73999999999999</v>
+        <v>89.03</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>2026</v>
       </c>
       <c r="V63" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>6728240000</v>
+        <v>7585360000</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -7824,24 +7824,24 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKU</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKU (695176)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKU</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -7855,19 +7855,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>79.62</v>
+        <v>71.36</v>
       </c>
       <c r="G64" t="n">
-        <v>90.36</v>
+        <v>99.48</v>
       </c>
       <c r="H64" t="n">
         <v>100</v>
@@ -7876,34 +7876,34 @@
         <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>59.23</v>
+        <v>42.72</v>
       </c>
       <c r="K64" t="n">
-        <v>81.44</v>
+        <v>98.95</v>
       </c>
       <c r="L64" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>100</v>
+      </c>
+      <c r="O64" t="n">
+        <v>100</v>
+      </c>
+      <c r="P64" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="Q64" t="n">
         <v>80</v>
       </c>
-      <c r="N64" t="n">
-        <v>100</v>
-      </c>
-      <c r="O64" t="n">
-        <v>100</v>
-      </c>
-      <c r="P64" t="n">
-        <v>88.17</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>100</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>88.17</v>
+        <v>89</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>2026</v>
       </c>
       <c r="V64" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -7932,33 +7932,33 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>6368000000</v>
+        <v>13489830000</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -7972,19 +7972,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>695176</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>76.69</v>
+        <v>72.23</v>
       </c>
       <c r="G65" t="n">
-        <v>92.92</v>
+        <v>96.34</v>
       </c>
       <c r="H65" t="n">
         <v>100</v>
@@ -7993,10 +7993,10 @@
         <v>100</v>
       </c>
       <c r="J65" t="n">
-        <v>53.38</v>
+        <v>44.45</v>
       </c>
       <c r="K65" t="n">
-        <v>71.68000000000001</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="L65" t="n">
         <v>100</v>
@@ -8011,7 +8011,7 @@
         <v>100</v>
       </c>
       <c r="P65" t="n">
-        <v>87.34</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="Q65" t="n">
         <v>100</v>
@@ -8020,7 +8020,7 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>87.34</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>2026</v>
       </c>
       <c r="V65" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>6314270000</v>
+        <v>6728240000</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -8058,24 +8058,24 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUT</t>
+          <t>KANTOR KEMENHAJ OKU</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUT (695182)</t>
+          <t>KANTOR KEMENHAJ OKU (695176)</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUT</t>
+          <t>KANTOR KEMENHAJ OKU</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -8089,19 +8089,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>695184</t>
+          <t>695182</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>75.98</v>
+        <v>76.69</v>
       </c>
       <c r="G66" t="n">
-        <v>88.78</v>
+        <v>92.92</v>
       </c>
       <c r="H66" t="n">
         <v>100</v>
@@ -8110,16 +8110,16 @@
         <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>51.95</v>
+        <v>53.38</v>
       </c>
       <c r="K66" t="n">
-        <v>88.43000000000001</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="L66" t="n">
         <v>100</v>
       </c>
       <c r="M66" t="n">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="N66" t="n">
         <v>100</v>
@@ -8128,7 +8128,7 @@
         <v>100</v>
       </c>
       <c r="P66" t="n">
-        <v>87.15000000000001</v>
+        <v>87.34</v>
       </c>
       <c r="Q66" t="n">
         <v>100</v>
@@ -8137,7 +8137,7 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>87.15000000000001</v>
+        <v>87.34</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>2026</v>
       </c>
       <c r="V66" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>6722660000</v>
+        <v>6314270000</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -8175,137 +8175,20 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUS</t>
+          <t>KANTOR KEMENHAJ OKUT</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUS (695184)</t>
+          <t>KANTOR KEMENHAJ OKUT (695182)</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUS</t>
+          <t>KANTOR KEMENHAJ OKUT</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>419006</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>79.72</v>
-      </c>
-      <c r="G67" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="H67" t="n">
-        <v>100</v>
-      </c>
-      <c r="I67" t="n">
-        <v>100</v>
-      </c>
-      <c r="J67" t="n">
-        <v>59.43</v>
-      </c>
-      <c r="K67" t="n">
-        <v>91.58</v>
-      </c>
-      <c r="L67" t="n">
-        <v>100</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>100</v>
-      </c>
-      <c r="O67" t="n">
-        <v>100</v>
-      </c>
-      <c r="P67" t="n">
-        <v>82.23</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>100</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
-        <v>82.23</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>JUNI</t>
-        </is>
-      </c>
-      <c r="U67" t="n">
-        <v>2026</v>
-      </c>
-      <c r="V67" t="n">
-        <v>45</v>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Upload</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>JUNI 2026</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="Z67" t="n">
-        <v>29335310000</v>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>SEDANG</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>BAWASLU OKU</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>BAWASLU OKU (419006)</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>BAWASLU OKU</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/IKPA_JUNI_2026.xlsx
+++ b/data/IKPA_JUNI_2026.xlsx
@@ -3553,7 +3553,7 @@
         <v>100</v>
       </c>
       <c r="L27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>100</v>
@@ -3565,16 +3565,16 @@
         <v>98.68000000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>99.67</v>
+        <v>89.67</v>
       </c>
       <c r="Q27" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>99.67</v>
+        <v>99.63</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/data/IKPA_JUNI_2026.xlsx
+++ b/data/IKPA_JUNI_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE66"/>
+  <dimension ref="A1:AE67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,7 +587,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -596,17 +596,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -678,33 +678,33 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>31572500000</v>
+        <v>5127100000</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK (692625)</t>
+          <t>PN BATURAJA (099228)</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -713,17 +713,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -795,26 +795,26 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>11480750000</v>
+        <v>970430000</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1213,10 +1213,10 @@
         <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
@@ -1225,10 +1225,10 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q7" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1263,33 +1263,33 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>64847500000</v>
+        <v>3127760000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (401944)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1298,17 +1298,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1330,10 +1330,10 @@
         <v>100</v>
       </c>
       <c r="L8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
@@ -1342,10 +1342,10 @@
         <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1380,26 +1380,26 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>139911100000</v>
+        <v>31572500000</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -1757,7 +1757,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1848,33 +1848,33 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>3127760000</v>
+        <v>11480750000</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1915,10 +1915,10 @@
         <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N13" t="n">
         <v>100</v>
@@ -1927,10 +1927,10 @@
         <v>100</v>
       </c>
       <c r="P13" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1965,26 +1965,26 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>970430000</v>
+        <v>139911100000</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440506)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
@@ -2927,7 +2927,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2936,24 +2936,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>99.92</v>
+        <v>100</v>
       </c>
       <c r="H22" t="n">
         <v>100</v>
@@ -2965,13 +2965,13 @@
         <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>99.84</v>
+        <v>100</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22" t="n">
         <v>100</v>
@@ -2980,16 +2980,16 @@
         <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>79.97</v>
+        <v>100</v>
       </c>
       <c r="Q22" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>99.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>2026</v>
       </c>
       <c r="V22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>67270440000</v>
+        <v>64847500000</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -3027,24 +3027,24 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418456)</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3053,24 +3053,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>99.87</v>
+        <v>99.92</v>
       </c>
       <c r="H23" t="n">
         <v>100</v>
@@ -3082,31 +3082,31 @@
         <v>100</v>
       </c>
       <c r="K23" t="n">
-        <v>99.73999999999999</v>
+        <v>99.84</v>
       </c>
       <c r="L23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>99.75</v>
+        <v>100</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
       </c>
       <c r="P23" t="n">
-        <v>99.92</v>
+        <v>79.97</v>
       </c>
       <c r="Q23" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>99.92</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>2026</v>
       </c>
       <c r="V23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3135,33 +3135,33 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>18312800000</v>
+        <v>67270440000</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>KEJARI  OKU (007130)</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3170,24 +3170,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KPU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>99.81999999999999</v>
+        <v>99.87</v>
       </c>
       <c r="H24" t="n">
         <v>100</v>
@@ -3199,31 +3199,31 @@
         <v>100</v>
       </c>
       <c r="K24" t="n">
-        <v>99.63</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>100</v>
+        <v>99.75</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
       </c>
       <c r="P24" t="n">
-        <v>79.93000000000001</v>
+        <v>99.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>99.91</v>
+        <v>99.92</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>2026</v>
       </c>
       <c r="V24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3252,33 +3252,33 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>43471570000</v>
+        <v>18312800000</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>KEJARI  OKU (007130)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3292,19 +3292,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KPU KABUPATEN OGAN KOMERING ULU</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>99.72</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
@@ -3316,7 +3316,7 @@
         <v>100</v>
       </c>
       <c r="K25" t="n">
-        <v>99.44</v>
+        <v>99.63</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3331,7 +3331,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="n">
-        <v>79.89</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>80</v>
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>99.86</v>
+        <v>99.91</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>2026</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3369,33 +3369,33 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>38902730000</v>
+        <v>43471570000</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3404,24 +3404,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>99.63</v>
+        <v>99.72</v>
       </c>
       <c r="H26" t="n">
         <v>100</v>
@@ -3433,7 +3433,7 @@
         <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>99.48999999999999</v>
+        <v>99.44</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3442,13 +3442,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>99.77</v>
+        <v>100</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
       </c>
       <c r="P26" t="n">
-        <v>79.88</v>
+        <v>79.89</v>
       </c>
       <c r="Q26" t="n">
         <v>80</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>99.84</v>
+        <v>99.86</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>2026</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3486,33 +3486,33 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>10710500000</v>
+        <v>38902730000</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3521,27 +3521,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>100</v>
+        <v>99.63</v>
       </c>
       <c r="H27" t="n">
-        <v>98.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
         <v>100</v>
@@ -3550,31 +3550,31 @@
         <v>100</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>100</v>
+        <v>99.77</v>
       </c>
       <c r="O27" t="n">
-        <v>98.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="P27" t="n">
-        <v>89.67</v>
+        <v>79.88</v>
       </c>
       <c r="Q27" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>99.63</v>
+        <v>99.84</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>2026</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>729500000</v>
+        <v>10710500000</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3612,24 +3612,24 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3638,27 +3638,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>99.48</v>
+        <v>100</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="I28" t="n">
         <v>100</v>
@@ -3667,10 +3667,10 @@
         <v>100</v>
       </c>
       <c r="K28" t="n">
-        <v>97.92</v>
+        <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>100</v>
@@ -3679,19 +3679,19 @@
         <v>100</v>
       </c>
       <c r="O28" t="n">
-        <v>100</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="P28" t="n">
-        <v>99.58</v>
+        <v>89.67</v>
       </c>
       <c r="Q28" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>99.58</v>
+        <v>99.63</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>2026</v>
       </c>
       <c r="V28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3720,33 +3720,33 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>105914680000</v>
+        <v>729500000</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3755,24 +3755,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>99.31999999999999</v>
+        <v>99.48</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -3784,7 +3784,7 @@
         <v>100</v>
       </c>
       <c r="K29" t="n">
-        <v>97.28</v>
+        <v>97.92</v>
       </c>
       <c r="L29" t="n">
         <v>100</v>
@@ -3793,13 +3793,13 @@
         <v>100</v>
       </c>
       <c r="N29" t="n">
-        <v>99.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>99.45999999999999</v>
+        <v>99.58</v>
       </c>
       <c r="Q29" t="n">
         <v>100</v>
@@ -3808,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>99.45999999999999</v>
+        <v>99.58</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>2026</v>
       </c>
       <c r="V29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3837,33 +3837,33 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>9346940000</v>
+        <v>105914680000</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3877,19 +3877,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>100</v>
       </c>
       <c r="G30" t="n">
-        <v>98.40000000000001</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
@@ -3901,31 +3901,31 @@
         <v>100</v>
       </c>
       <c r="K30" t="n">
-        <v>96.8</v>
+        <v>97.28</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30" t="n">
-        <v>100</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>79.36</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>99.2</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>2026</v>
       </c>
       <c r="V30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>3898470000</v>
+        <v>9346940000</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3963,24 +3963,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3989,24 +3989,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>98.75</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
@@ -4018,13 +4018,13 @@
         <v>100</v>
       </c>
       <c r="K31" t="n">
-        <v>94.98</v>
+        <v>96.8</v>
       </c>
       <c r="L31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>100</v>
@@ -4033,16 +4033,16 @@
         <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>99</v>
+        <v>79.36</v>
       </c>
       <c r="Q31" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>2026</v>
       </c>
       <c r="V31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -4071,33 +4071,33 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>38391890000</v>
+        <v>3898470000</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4106,24 +4106,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KPU KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>96.92</v>
+        <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>99.98</v>
+        <v>98.75</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
@@ -4132,16 +4132,16 @@
         <v>100</v>
       </c>
       <c r="J32" t="n">
-        <v>93.83</v>
+        <v>100</v>
       </c>
       <c r="K32" t="n">
-        <v>99.95</v>
+        <v>94.98</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N32" t="n">
         <v>100</v>
@@ -4150,16 +4150,16 @@
         <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>79.06</v>
+        <v>99</v>
       </c>
       <c r="Q32" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>98.83</v>
+        <v>99</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>2026</v>
       </c>
       <c r="V32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>39931940000</v>
+        <v>38391890000</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4197,24 +4197,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4223,24 +4223,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>100</v>
+        <v>96.92</v>
       </c>
       <c r="G33" t="n">
-        <v>98.45999999999999</v>
+        <v>99.98</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
@@ -4249,16 +4249,16 @@
         <v>100</v>
       </c>
       <c r="J33" t="n">
-        <v>100</v>
+        <v>93.83</v>
       </c>
       <c r="K33" t="n">
-        <v>93.84</v>
+        <v>99.95</v>
       </c>
       <c r="L33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>100</v>
@@ -4267,16 +4267,16 @@
         <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>98.77</v>
+        <v>79.06</v>
       </c>
       <c r="Q33" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>98.77</v>
+        <v>98.83</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>2026</v>
       </c>
       <c r="V33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4305,33 +4305,33 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>3127020000</v>
+        <v>39931940000</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4340,24 +4340,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>96.09</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>100</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -4366,16 +4366,16 @@
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>92.17</v>
+        <v>100</v>
       </c>
       <c r="K34" t="n">
-        <v>100</v>
+        <v>93.84</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N34" t="n">
         <v>100</v>
@@ -4384,16 +4384,16 @@
         <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>78.83</v>
+        <v>98.77</v>
       </c>
       <c r="Q34" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>98.53</v>
+        <v>98.77</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>2026</v>
       </c>
       <c r="V34" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>5172810000</v>
+        <v>3127020000</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -4431,24 +4431,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4457,24 +4457,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>100</v>
+        <v>96.09</v>
       </c>
       <c r="G35" t="n">
-        <v>98.14</v>
+        <v>100</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -4483,16 +4483,16 @@
         <v>100</v>
       </c>
       <c r="J35" t="n">
-        <v>100</v>
+        <v>92.17</v>
       </c>
       <c r="K35" t="n">
-        <v>92.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="L35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>100</v>
@@ -4501,16 +4501,16 @@
         <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>98.51000000000001</v>
+        <v>78.83</v>
       </c>
       <c r="Q35" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>98.51000000000001</v>
+        <v>98.53</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>2026</v>
       </c>
       <c r="V35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4539,33 +4539,33 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>10808640000</v>
+        <v>5172810000</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440504)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4574,24 +4574,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>94.89</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>100</v>
+        <v>98.14</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
@@ -4600,10 +4600,10 @@
         <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>89.78</v>
+        <v>100</v>
       </c>
       <c r="K36" t="n">
-        <v>100</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="L36" t="n">
         <v>100</v>
@@ -4618,7 +4618,7 @@
         <v>100</v>
       </c>
       <c r="P36" t="n">
-        <v>98.47</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="Q36" t="n">
         <v>100</v>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>98.47</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>2026</v>
       </c>
       <c r="V36" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>20452310000</v>
+        <v>10808640000</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4665,24 +4665,24 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4691,24 +4691,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>100</v>
+        <v>94.89</v>
       </c>
       <c r="G37" t="n">
-        <v>97.92</v>
+        <v>100</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -4717,10 +4717,10 @@
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>100</v>
+        <v>89.78</v>
       </c>
       <c r="K37" t="n">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="L37" t="n">
         <v>100</v>
@@ -4735,7 +4735,7 @@
         <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>98.33</v>
+        <v>98.47</v>
       </c>
       <c r="Q37" t="n">
         <v>100</v>
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>98.33</v>
+        <v>98.47</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>2026</v>
       </c>
       <c r="V37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4773,33 +4773,33 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>61767300000</v>
+        <v>20452310000</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4808,24 +4808,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>94.28</v>
+        <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>100</v>
+        <v>97.92</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
@@ -4834,10 +4834,10 @@
         <v>100</v>
       </c>
       <c r="J38" t="n">
-        <v>88.56</v>
+        <v>100</v>
       </c>
       <c r="K38" t="n">
-        <v>100</v>
+        <v>91.67</v>
       </c>
       <c r="L38" t="n">
         <v>100</v>
@@ -4852,7 +4852,7 @@
         <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>98.28</v>
+        <v>98.33</v>
       </c>
       <c r="Q38" t="n">
         <v>100</v>
@@ -4861,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>98.28</v>
+        <v>98.33</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>2026</v>
       </c>
       <c r="V38" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>128489370000</v>
+        <v>61767300000</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4899,24 +4899,24 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4925,24 +4925,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
+        <v>94.28</v>
       </c>
       <c r="G39" t="n">
-        <v>96.36</v>
+        <v>100</v>
       </c>
       <c r="H39" t="n">
         <v>100</v>
@@ -4951,16 +4951,16 @@
         <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>100</v>
+        <v>88.56</v>
       </c>
       <c r="K39" t="n">
-        <v>92.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N39" t="n">
         <v>100</v>
@@ -4969,16 +4969,16 @@
         <v>100</v>
       </c>
       <c r="P39" t="n">
-        <v>78.54000000000001</v>
+        <v>98.28</v>
       </c>
       <c r="Q39" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>98.18000000000001</v>
+        <v>98.28</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>2026</v>
       </c>
       <c r="V39" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -5007,33 +5007,33 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>1731600000</v>
+        <v>128489370000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5047,19 +5047,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>94.25</v>
+        <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>99.66</v>
+        <v>96.36</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
@@ -5068,16 +5068,16 @@
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>88.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="K40" t="n">
-        <v>98.62</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>100</v>
@@ -5086,16 +5086,16 @@
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>98</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="Q40" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>98</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>2026</v>
       </c>
       <c r="V40" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>9098870000</v>
+        <v>1731600000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -5133,24 +5133,24 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5159,24 +5159,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>96.73</v>
+        <v>94.25</v>
       </c>
       <c r="G41" t="n">
-        <v>98.70999999999999</v>
+        <v>99.66</v>
       </c>
       <c r="H41" t="n">
         <v>100</v>
@@ -5185,10 +5185,10 @@
         <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>93.45</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>94.84999999999999</v>
+        <v>98.62</v>
       </c>
       <c r="L41" t="n">
         <v>100</v>
@@ -5203,7 +5203,7 @@
         <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>97.98999999999999</v>
+        <v>98</v>
       </c>
       <c r="Q41" t="n">
         <v>100</v>
@@ -5212,7 +5212,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>97.98999999999999</v>
+        <v>98</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>2026</v>
       </c>
       <c r="V41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -5241,33 +5241,33 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>37327090000</v>
+        <v>9098870000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5276,24 +5276,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>92.62</v>
+        <v>96.73</v>
       </c>
       <c r="G42" t="n">
-        <v>99.47</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -5302,10 +5302,10 @@
         <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>85.23999999999999</v>
+        <v>93.45</v>
       </c>
       <c r="K42" t="n">
-        <v>98.41</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="L42" t="n">
         <v>100</v>
@@ -5314,22 +5314,22 @@
         <v>100</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O42" t="n">
         <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>87.47</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="Q42" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>97.19</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>2026</v>
       </c>
       <c r="V42" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5358,33 +5358,33 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>287629890000</v>
+        <v>37327090000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5398,19 +5398,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>92.5</v>
+        <v>92.62</v>
       </c>
       <c r="G43" t="n">
-        <v>98.52</v>
+        <v>99.47</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
@@ -5419,10 +5419,10 @@
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>84.98999999999999</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>99.88</v>
+        <v>98.41</v>
       </c>
       <c r="L43" t="n">
         <v>100</v>
@@ -5431,22 +5431,22 @@
         <v>100</v>
       </c>
       <c r="N43" t="n">
-        <v>94.20999999999999</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>97.15000000000001</v>
+        <v>87.47</v>
       </c>
       <c r="Q43" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>97.15000000000001</v>
+        <v>97.19</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>2026</v>
       </c>
       <c r="V43" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>405581540000</v>
+        <v>287629890000</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -5484,24 +5484,24 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5510,24 +5510,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>92.8</v>
+        <v>92.5</v>
       </c>
       <c r="G44" t="n">
-        <v>99.04000000000001</v>
+        <v>98.52</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
@@ -5536,10 +5536,10 @@
         <v>100</v>
       </c>
       <c r="J44" t="n">
-        <v>85.59999999999999</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>96.15000000000001</v>
+        <v>99.88</v>
       </c>
       <c r="L44" t="n">
         <v>100</v>
@@ -5548,13 +5548,13 @@
         <v>100</v>
       </c>
       <c r="N44" t="n">
-        <v>100</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="O44" t="n">
         <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>97.06999999999999</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="Q44" t="n">
         <v>100</v>
@@ -5563,7 +5563,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>97.06999999999999</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>2026</v>
       </c>
       <c r="V44" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5592,33 +5592,33 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>16133240000</v>
+        <v>405581540000</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5627,24 +5627,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>92.43000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="G45" t="n">
-        <v>99.18000000000001</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="H45" t="n">
         <v>100</v>
@@ -5653,10 +5653,10 @@
         <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>84.84999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>96.72</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="L45" t="n">
         <v>100</v>
@@ -5709,7 +5709,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>14214110000</v>
+        <v>16133240000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -5718,24 +5718,24 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5744,24 +5744,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>89.40000000000001</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>99.92</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
@@ -5770,10 +5770,10 @@
         <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>78.8</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>99.66</v>
+        <v>96.72</v>
       </c>
       <c r="L46" t="n">
         <v>100</v>
@@ -5788,7 +5788,7 @@
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>96.75</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="Q46" t="n">
         <v>100</v>
@@ -5797,7 +5797,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>96.75</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>2026</v>
       </c>
       <c r="V46" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>40484710000</v>
+        <v>14214110000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5835,24 +5835,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5861,24 +5861,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>89.62</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>98.31</v>
+        <v>99.92</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -5887,13 +5887,13 @@
         <v>100</v>
       </c>
       <c r="J47" t="n">
-        <v>79.23</v>
+        <v>78.8</v>
       </c>
       <c r="K47" t="n">
-        <v>99.91</v>
+        <v>99.66</v>
       </c>
       <c r="L47" t="n">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="M47" t="n">
         <v>100</v>
@@ -5905,7 +5905,7 @@
         <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>96.2</v>
+        <v>96.75</v>
       </c>
       <c r="Q47" t="n">
         <v>100</v>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>96.2</v>
+        <v>96.75</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>2026</v>
       </c>
       <c r="V47" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>15177700000</v>
+        <v>40484710000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5952,24 +5952,24 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5978,24 +5978,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>88.25</v>
+        <v>89.62</v>
       </c>
       <c r="G48" t="n">
-        <v>99.54000000000001</v>
+        <v>98.31</v>
       </c>
       <c r="H48" t="n">
         <v>100</v>
@@ -6004,13 +6004,13 @@
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>76.48999999999999</v>
+        <v>79.23</v>
       </c>
       <c r="K48" t="n">
-        <v>98.17</v>
+        <v>99.91</v>
       </c>
       <c r="L48" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="M48" t="n">
         <v>100</v>
@@ -6022,7 +6022,7 @@
         <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>96.11</v>
+        <v>96.2</v>
       </c>
       <c r="Q48" t="n">
         <v>100</v>
@@ -6031,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>96.11</v>
+        <v>96.2</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>2026</v>
       </c>
       <c r="V48" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>31225620000</v>
+        <v>15177700000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -6069,24 +6069,24 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6095,24 +6095,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>88.22</v>
+        <v>88.25</v>
       </c>
       <c r="G49" t="n">
-        <v>100</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
@@ -6121,16 +6121,16 @@
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>76.43000000000001</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>100</v>
+        <v>98.17</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N49" t="n">
         <v>100</v>
@@ -6139,16 +6139,16 @@
         <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>76.45999999999999</v>
+        <v>96.11</v>
       </c>
       <c r="Q49" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>95.58</v>
+        <v>96.11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>2026</v>
       </c>
       <c r="V49" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -6177,33 +6177,33 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>5176090000</v>
+        <v>31225620000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6212,24 +6212,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>88.09999999999999</v>
+        <v>88.22</v>
       </c>
       <c r="G50" t="n">
-        <v>98.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="H50" t="n">
         <v>100</v>
@@ -6238,16 +6238,16 @@
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>76.2</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>94.61</v>
+        <v>100</v>
       </c>
       <c r="L50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
         <v>100</v>
@@ -6256,16 +6256,16 @@
         <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>95.34999999999999</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="Q50" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>95.34999999999999</v>
+        <v>95.58</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>2026</v>
       </c>
       <c r="V50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -6294,33 +6294,33 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>74397990000</v>
+        <v>5176090000</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6334,19 +6334,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>95.89</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>93.37</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="H51" t="n">
         <v>100</v>
@@ -6355,16 +6355,16 @@
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>91.78</v>
+        <v>76.2</v>
       </c>
       <c r="K51" t="n">
-        <v>86.73999999999999</v>
+        <v>94.61</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N51" t="n">
         <v>100</v>
@@ -6373,16 +6373,16 @@
         <v>100</v>
       </c>
       <c r="P51" t="n">
-        <v>76.12</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="Q51" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>95.14</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>2026</v>
       </c>
       <c r="V51" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>50054370000</v>
+        <v>74397990000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -6420,24 +6420,24 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6446,24 +6446,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>93.68000000000001</v>
+        <v>95.89</v>
       </c>
       <c r="G52" t="n">
-        <v>93.70999999999999</v>
+        <v>93.37</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -6472,10 +6472,10 @@
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>87.36</v>
+        <v>91.78</v>
       </c>
       <c r="K52" t="n">
-        <v>87.42</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -6490,7 +6490,7 @@
         <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>75.59</v>
+        <v>76.12</v>
       </c>
       <c r="Q52" t="n">
         <v>80</v>
@@ -6499,7 +6499,7 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>94.48999999999999</v>
+        <v>95.14</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>2026</v>
       </c>
       <c r="V52" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -6528,33 +6528,33 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>7789580000</v>
+        <v>50054370000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6563,24 +6563,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>94.68000000000001</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>94.77</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="H53" t="n">
         <v>100</v>
@@ -6589,16 +6589,16 @@
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>89.36</v>
+        <v>87.36</v>
       </c>
       <c r="K53" t="n">
-        <v>79.09</v>
+        <v>87.42</v>
       </c>
       <c r="L53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>100</v>
@@ -6607,16 +6607,16 @@
         <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>94.22</v>
+        <v>75.59</v>
       </c>
       <c r="Q53" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>94.22</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>2026</v>
       </c>
       <c r="V53" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -6645,33 +6645,33 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>114852670000</v>
+        <v>7789580000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6680,24 +6680,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>87.65000000000001</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>96.15000000000001</v>
+        <v>94.77</v>
       </c>
       <c r="H54" t="n">
         <v>100</v>
@@ -6706,10 +6706,10 @@
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>75.29000000000001</v>
+        <v>89.36</v>
       </c>
       <c r="K54" t="n">
-        <v>84.61</v>
+        <v>79.09</v>
       </c>
       <c r="L54" t="n">
         <v>100</v>
@@ -6724,7 +6724,7 @@
         <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>93.22</v>
+        <v>94.22</v>
       </c>
       <c r="Q54" t="n">
         <v>100</v>
@@ -6733,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>93.22</v>
+        <v>94.22</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>2026</v>
       </c>
       <c r="V54" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6762,33 +6762,33 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>13427580000</v>
+        <v>114852670000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6802,19 +6802,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>82.70999999999999</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>99.05</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -6823,16 +6823,16 @@
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>65.42</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>98.09999999999999</v>
+        <v>84.61</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N55" t="n">
         <v>100</v>
@@ -6841,16 +6841,16 @@
         <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>74.43000000000001</v>
+        <v>93.22</v>
       </c>
       <c r="Q55" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>93.04000000000001</v>
+        <v>93.22</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>2026</v>
       </c>
       <c r="V55" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6879,33 +6879,33 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>9731020000</v>
+        <v>13427580000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6919,19 +6919,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>86.23999999999999</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>95.86</v>
+        <v>99.05</v>
       </c>
       <c r="H56" t="n">
         <v>100</v>
@@ -6940,16 +6940,16 @@
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>72.48</v>
+        <v>65.42</v>
       </c>
       <c r="K56" t="n">
-        <v>83.44</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>100</v>
@@ -6958,16 +6958,16 @@
         <v>100</v>
       </c>
       <c r="P56" t="n">
-        <v>92.56</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="Q56" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>92.56</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>2026</v>
       </c>
       <c r="V56" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -6996,33 +6996,33 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>20589110000</v>
+        <v>9731020000</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -7036,19 +7036,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>100</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>84.53</v>
+        <v>95.86</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
@@ -7057,16 +7057,16 @@
         <v>100</v>
       </c>
       <c r="J57" t="n">
-        <v>100</v>
+        <v>72.48</v>
       </c>
       <c r="K57" t="n">
-        <v>69.05</v>
+        <v>83.44</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N57" t="n">
         <v>100</v>
@@ -7075,16 +7075,16 @@
         <v>100</v>
       </c>
       <c r="P57" t="n">
-        <v>73.81</v>
+        <v>92.56</v>
       </c>
       <c r="Q57" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>92.26000000000001</v>
+        <v>92.56</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>2026</v>
       </c>
       <c r="V57" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>15707450000</v>
+        <v>20589110000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -7122,24 +7122,24 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -7148,24 +7148,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>79.72</v>
+        <v>100</v>
       </c>
       <c r="G58" t="n">
-        <v>97.90000000000001</v>
+        <v>84.53</v>
       </c>
       <c r="H58" t="n">
         <v>100</v>
@@ -7174,16 +7174,16 @@
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>59.43</v>
+        <v>100</v>
       </c>
       <c r="K58" t="n">
-        <v>91.58</v>
+        <v>69.05</v>
       </c>
       <c r="L58" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
         <v>100</v>
@@ -7192,16 +7192,16 @@
         <v>100</v>
       </c>
       <c r="P58" t="n">
-        <v>92.23</v>
+        <v>73.81</v>
       </c>
       <c r="Q58" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>92.23</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>2026</v>
       </c>
       <c r="V58" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>29335310000</v>
+        <v>15707450000</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -7239,24 +7239,24 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -7265,24 +7265,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>85.63</v>
+        <v>79.72</v>
       </c>
       <c r="G59" t="n">
-        <v>94.89</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H59" t="n">
         <v>100</v>
@@ -7291,16 +7291,16 @@
         <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>71.26000000000001</v>
+        <v>59.43</v>
       </c>
       <c r="K59" t="n">
-        <v>89.77</v>
+        <v>91.58</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N59" t="n">
         <v>100</v>
@@ -7309,16 +7309,16 @@
         <v>100</v>
       </c>
       <c r="P59" t="n">
-        <v>73.64</v>
+        <v>92.23</v>
       </c>
       <c r="Q59" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>92.05</v>
+        <v>92.23</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>2026</v>
       </c>
       <c r="V59" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -7347,33 +7347,33 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>5671610000</v>
+        <v>29335310000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -7387,19 +7387,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>84.84</v>
+        <v>85.63</v>
       </c>
       <c r="G60" t="n">
-        <v>94.43000000000001</v>
+        <v>94.89</v>
       </c>
       <c r="H60" t="n">
         <v>100</v>
@@ -7408,34 +7408,34 @@
         <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>69.67</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>77.98</v>
+        <v>89.77</v>
       </c>
       <c r="L60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>99.72</v>
+        <v>100</v>
       </c>
       <c r="O60" t="n">
         <v>100</v>
       </c>
       <c r="P60" t="n">
-        <v>91.02</v>
+        <v>73.64</v>
       </c>
       <c r="Q60" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>91.02</v>
+        <v>92.05</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>2026</v>
       </c>
       <c r="V60" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>4481070000</v>
+        <v>5671610000</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -7473,24 +7473,24 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT (597480)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -7499,24 +7499,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>695184</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>75.98</v>
+        <v>84.84</v>
       </c>
       <c r="G61" t="n">
-        <v>97.11</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="H61" t="n">
         <v>100</v>
@@ -7525,10 +7525,10 @@
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>51.95</v>
+        <v>69.67</v>
       </c>
       <c r="K61" t="n">
-        <v>88.43000000000001</v>
+        <v>77.98</v>
       </c>
       <c r="L61" t="n">
         <v>100</v>
@@ -7537,13 +7537,13 @@
         <v>100</v>
       </c>
       <c r="N61" t="n">
-        <v>100</v>
+        <v>99.72</v>
       </c>
       <c r="O61" t="n">
         <v>100</v>
       </c>
       <c r="P61" t="n">
-        <v>90.48</v>
+        <v>91.02</v>
       </c>
       <c r="Q61" t="n">
         <v>100</v>
@@ -7552,7 +7552,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>90.48</v>
+        <v>91.02</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>2026</v>
       </c>
       <c r="V61" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>6722660000</v>
+        <v>4481070000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -7590,24 +7590,24 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUS</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUS (695184)</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUS</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -7616,24 +7616,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>695184</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>79.62</v>
+        <v>75.98</v>
       </c>
       <c r="G62" t="n">
-        <v>95.36</v>
+        <v>97.11</v>
       </c>
       <c r="H62" t="n">
         <v>100</v>
@@ -7642,10 +7642,10 @@
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>59.23</v>
+        <v>51.95</v>
       </c>
       <c r="K62" t="n">
-        <v>81.44</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="L62" t="n">
         <v>100</v>
@@ -7660,7 +7660,7 @@
         <v>100</v>
       </c>
       <c r="P62" t="n">
-        <v>90.17</v>
+        <v>90.48</v>
       </c>
       <c r="Q62" t="n">
         <v>100</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>90.17</v>
+        <v>90.48</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>2026</v>
       </c>
       <c r="V62" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>6368000000</v>
+        <v>6722660000</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -7707,24 +7707,24 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KANTOR KEMENHAJ OKUS</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>KANTOR KEMENHAJ OKUS (695184)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KANTOR KEMENHAJ OKUS</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -7738,19 +7738,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>79.63</v>
+        <v>79.62</v>
       </c>
       <c r="G63" t="n">
-        <v>93.34999999999999</v>
+        <v>95.36</v>
       </c>
       <c r="H63" t="n">
         <v>100</v>
@@ -7759,16 +7759,16 @@
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>59.26</v>
+        <v>59.23</v>
       </c>
       <c r="K63" t="n">
-        <v>86.69</v>
+        <v>81.44</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N63" t="n">
         <v>100</v>
@@ -7777,16 +7777,16 @@
         <v>100</v>
       </c>
       <c r="P63" t="n">
-        <v>71.23</v>
+        <v>90.17</v>
       </c>
       <c r="Q63" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>89.03</v>
+        <v>90.17</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>2026</v>
       </c>
       <c r="V63" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>7585360000</v>
+        <v>6368000000</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -7824,24 +7824,24 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -7855,19 +7855,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>71.36</v>
+        <v>79.63</v>
       </c>
       <c r="G64" t="n">
-        <v>99.48</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="H64" t="n">
         <v>100</v>
@@ -7876,10 +7876,10 @@
         <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>42.72</v>
+        <v>59.26</v>
       </c>
       <c r="K64" t="n">
-        <v>98.95</v>
+        <v>86.69</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -7894,7 +7894,7 @@
         <v>100</v>
       </c>
       <c r="P64" t="n">
-        <v>71.2</v>
+        <v>71.23</v>
       </c>
       <c r="Q64" t="n">
         <v>80</v>
@@ -7903,7 +7903,7 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>89</v>
+        <v>89.03</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>2026</v>
       </c>
       <c r="V64" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -7932,33 +7932,33 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>13489830000</v>
+        <v>7585360000</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -7967,24 +7967,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>695176</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>72.23</v>
+        <v>71.36</v>
       </c>
       <c r="G65" t="n">
-        <v>96.34</v>
+        <v>99.48</v>
       </c>
       <c r="H65" t="n">
         <v>100</v>
@@ -7993,16 +7993,16 @@
         <v>100</v>
       </c>
       <c r="J65" t="n">
-        <v>44.45</v>
+        <v>42.72</v>
       </c>
       <c r="K65" t="n">
-        <v>85.34999999999999</v>
+        <v>98.95</v>
       </c>
       <c r="L65" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
         <v>100</v>
@@ -8011,16 +8011,16 @@
         <v>100</v>
       </c>
       <c r="P65" t="n">
-        <v>88.73999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="Q65" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>88.73999999999999</v>
+        <v>89</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>2026</v>
       </c>
       <c r="V65" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -8049,33 +8049,33 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>6728240000</v>
+        <v>13489830000</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKU</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKU (695176)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKU</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -8089,19 +8089,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>695176</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>76.69</v>
+        <v>72.23</v>
       </c>
       <c r="G66" t="n">
-        <v>92.92</v>
+        <v>96.34</v>
       </c>
       <c r="H66" t="n">
         <v>100</v>
@@ -8110,10 +8110,10 @@
         <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>53.38</v>
+        <v>44.45</v>
       </c>
       <c r="K66" t="n">
-        <v>71.68000000000001</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="L66" t="n">
         <v>100</v>
@@ -8128,7 +8128,7 @@
         <v>100</v>
       </c>
       <c r="P66" t="n">
-        <v>87.34</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="Q66" t="n">
         <v>100</v>
@@ -8137,7 +8137,7 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>87.34</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8148,47 +8148,164 @@
         <v>2026</v>
       </c>
       <c r="V66" t="n">
+        <v>44</v>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>JUNI 2026</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>6728240000</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENHAJ OKU</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENHAJ OKU (695176)</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENHAJ OKU</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>695182</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>76.69</v>
+      </c>
+      <c r="G67" t="n">
+        <v>92.92</v>
+      </c>
+      <c r="H67" t="n">
+        <v>100</v>
+      </c>
+      <c r="I67" t="n">
+        <v>100</v>
+      </c>
+      <c r="J67" t="n">
+        <v>53.38</v>
+      </c>
+      <c r="K67" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="L67" t="n">
+        <v>100</v>
+      </c>
+      <c r="M67" t="n">
+        <v>100</v>
+      </c>
+      <c r="N67" t="n">
+        <v>100</v>
+      </c>
+      <c r="O67" t="n">
+        <v>100</v>
+      </c>
+      <c r="P67" t="n">
+        <v>87.34</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>100</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>87.34</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>JUNI</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V67" t="n">
         <v>45</v>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>JUNI 2026</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="Z66" t="n">
+      <c r="Z67" t="n">
         <v>6314270000</v>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>KANTOR KEMENHAJ OKUT</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
+      <c r="AC67" t="inlineStr">
         <is>
           <t>KANTOR KEMENHAJ OKUT (695182)</t>
         </is>
       </c>
-      <c r="AD66" t="inlineStr">
+      <c r="AD67" t="inlineStr">
         <is>
           <t>KANTOR KEMENHAJ OKUT</t>
         </is>
       </c>
-      <c r="AE66" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
